--- a/public/richtwerte/statsfinity-deckbuilding-benchmarks-en.xlsx
+++ b/public/richtwerte/statsfinity-deckbuilding-benchmarks-en.xlsx
@@ -133,7 +133,7 @@
     <t>Average number drawn</t>
   </si>
   <si>
-    <t>cEDH</t>
+    <t>Fast Mana</t>
   </si>
   <si>
     <t>Low curve</t>
